--- a/processing_scripts/Inventory_Processing/2022 Metadata Creation/T4 TMP Data Sheet.xlsx
+++ b/processing_scripts/Inventory_Processing/2022 Metadata Creation/T4 TMP Data Sheet.xlsx
@@ -36,10 +36,13 @@
     <t>Personnel:</t>
   </si>
   <si>
+    <t>AES</t>
+  </si>
+  <si>
     <t>EP</t>
   </si>
   <si>
-    <t>AES</t>
+    <t>MKB</t>
   </si>
   <si>
     <t>Depth: 15cm</t>
@@ -99,6 +102,9 @@
     <t>Notes</t>
   </si>
   <si>
+    <t>Total Volume</t>
+  </si>
+  <si>
     <t>Total Vol</t>
   </si>
   <si>
@@ -108,12 +114,15 @@
     <t>Evacuated (cb)</t>
   </si>
   <si>
+    <t>FRESHWATER</t>
+  </si>
+  <si>
+    <t>SEAWATER</t>
+  </si>
+  <si>
     <t xml:space="preserve">CONTROL </t>
   </si>
   <si>
-    <t>FRESHWATER</t>
-  </si>
-  <si>
     <t>C3</t>
   </si>
   <si>
@@ -126,9 +135,6 @@
     <t>F4</t>
   </si>
   <si>
-    <t>MKB</t>
-  </si>
-  <si>
     <t>H3</t>
   </si>
   <si>
@@ -148,12 +154,6 @@
   </si>
   <si>
     <t>I5</t>
-  </si>
-  <si>
-    <t>Total Volume</t>
-  </si>
-  <si>
-    <t>SEAWATER</t>
   </si>
 </sst>
 </file>
@@ -161,8 +161,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="M/d/yyyy"/>
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="165" formatCode="M/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="h&quot;:&quot;mm"/>
   </numFmts>
   <fonts count="5">
@@ -199,8 +199,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor theme="4"/>
+        <fgColor rgb="FF00DA63"/>
+        <bgColor rgb="FF00DA63"/>
       </patternFill>
     </fill>
     <fill>
@@ -211,14 +211,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFA7"/>
-        <bgColor rgb="FFFFFFA7"/>
+        <fgColor theme="5"/>
+        <bgColor theme="5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00DA63"/>
-        <bgColor rgb="FF00DA63"/>
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFA7"/>
+        <bgColor rgb="FFFFFFA7"/>
       </patternFill>
     </fill>
     <fill>
@@ -237,12 +243,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor theme="5"/>
       </patternFill>
     </fill>
     <fill>
@@ -346,39 +346,42 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
     <xf borderId="2" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="3" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -395,15 +398,15 @@
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
-    </xf>
     <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
@@ -414,26 +417,32 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="1" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
@@ -446,26 +455,17 @@
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="2" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="8" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
+    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -502,15 +502,15 @@
     </dxf>
   </dxfs>
   <tableStyles count="3">
-    <tableStyle count="2" pivot="0" name="FRESHWATER-style">
-      <tableStyleElement dxfId="1" type="firstRowStripe"/>
-      <tableStyleElement dxfId="2" type="secondRowStripe"/>
-    </tableStyle>
     <tableStyle count="2" pivot="0" name="CONTROL-style">
       <tableStyleElement dxfId="1" type="firstRowStripe"/>
       <tableStyleElement dxfId="2" type="secondRowStripe"/>
     </tableStyle>
     <tableStyle count="2" pivot="0" name="SEAWATER-style">
+      <tableStyleElement dxfId="1" type="firstRowStripe"/>
+      <tableStyleElement dxfId="2" type="secondRowStripe"/>
+    </tableStyle>
+    <tableStyle count="2" pivot="0" name="FRESHWATER-style">
       <tableStyleElement dxfId="1" type="firstRowStripe"/>
       <tableStyleElement dxfId="2" type="secondRowStripe"/>
     </tableStyle>
@@ -535,7 +535,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C8:N17" displayName="Table_2" name="Table_2" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C8:N17" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="12">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -555,7 +555,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D8:N17" displayName="Table_1" name="Table_1" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D8:N17" displayName="Table_2" name="Table_2" id="3">
   <tableColumns count="11">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -574,7 +574,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C8:N17" displayName="Table_3" name="Table_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C8:N17" displayName="Table_3" name="Table_3" id="2">
   <tableColumns count="12">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -834,19 +834,19 @@
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="6">
         <v>44736.0</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="8">
         <v>0.5</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="9" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="2"/>
@@ -862,8 +862,8 @@
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>7</v>
+      <c r="B4" s="9" t="s">
+        <v>8</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -880,7 +880,7 @@
     </row>
     <row r="5">
       <c r="A5" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -897,494 +897,494 @@
       <c r="N5" s="3"/>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="s">
-        <v>10</v>
+      <c r="A6" s="11" t="s">
+        <v>11</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="D6" s="16"/>
+      <c r="E6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="F6" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="15"/>
-      <c r="I6" s="20" t="s">
+      <c r="G6" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="15"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="22" t="s">
+      <c r="H6" s="16"/>
+      <c r="I6" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="M6" s="23"/>
-      <c r="N6" s="15"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" s="24"/>
+      <c r="N6" s="16"/>
     </row>
     <row r="7">
-      <c r="A7" s="24"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="25" t="s">
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="D7" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="E7" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="28" t="s">
+      <c r="F7" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="G7" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="H7" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="J7" s="29" t="s">
+      <c r="I7" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="K7" s="30" t="s">
+      <c r="J7" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="L7" s="31" t="s">
+      <c r="K7" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="M7" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="N7" s="31" t="s">
-        <v>30</v>
+      <c r="L7" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="N7" s="32" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I8" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="J8" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="M8" s="37">
+      <c r="A8" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="40"/>
+      <c r="L8" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="M8" s="39">
         <v>0.0</v>
       </c>
-      <c r="N8" s="37" t="s">
-        <v>34</v>
+      <c r="N8" s="39" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="39" t="s">
+      <c r="A9" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="I9" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="J9" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="K9" s="38"/>
-      <c r="L9" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="M9" s="42">
+      <c r="B9" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9" s="45">
         <v>0.0</v>
       </c>
-      <c r="N9" s="42" t="s">
-        <v>34</v>
+      <c r="N9" s="45" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I10" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="J10" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K10" s="38"/>
-      <c r="L10" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="M10" s="37" t="s">
+      <c r="A10" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I10" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="N10" s="37" t="s">
-        <v>34</v>
+      <c r="N10" s="39" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="41">
+      <c r="A11" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="44">
         <v>10.0</v>
       </c>
-      <c r="D11" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="42">
+      <c r="D11" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="45">
         <v>1.5</v>
       </c>
-      <c r="F11" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="I11" s="41">
+      <c r="F11" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="44">
         <v>12.5</v>
       </c>
-      <c r="J11" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="M11" s="42">
+      <c r="J11" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" s="40"/>
+      <c r="L11" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="M11" s="45">
         <v>24.0</v>
       </c>
-      <c r="N11" s="42">
+      <c r="N11" s="45">
         <v>50.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="36">
+      <c r="A12" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="37">
         <v>10.0</v>
       </c>
-      <c r="D12" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="37">
+      <c r="D12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="39">
         <v>1.5</v>
       </c>
-      <c r="F12" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I12" s="36">
+      <c r="F12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="37">
         <v>25.0</v>
       </c>
-      <c r="J12" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="M12" s="37">
+      <c r="J12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" s="40"/>
+      <c r="L12" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="M12" s="39">
         <v>40.0</v>
       </c>
-      <c r="N12" s="37">
+      <c r="N12" s="39">
         <v>50.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="H13" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="I13" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="J13" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="K13" s="38"/>
-      <c r="L13" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="M13" s="42">
+      <c r="A13" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" s="40"/>
+      <c r="L13" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="M13" s="45">
         <v>0.0</v>
       </c>
-      <c r="N13" s="42" t="s">
-        <v>34</v>
+      <c r="N13" s="45" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="36">
+      <c r="A14" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="37">
         <v>10.0</v>
       </c>
-      <c r="D14" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="37">
+      <c r="D14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="39">
         <v>1.5</v>
       </c>
-      <c r="F14" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H14" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I14" s="36">
+      <c r="F14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" s="37">
         <v>25.0</v>
       </c>
-      <c r="J14" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K14" s="38"/>
-      <c r="L14" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="M14" s="37">
+      <c r="J14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="40"/>
+      <c r="L14" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="M14" s="39">
         <v>42.0</v>
       </c>
-      <c r="N14" s="37">
+      <c r="N14" s="39">
         <v>50.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="41">
+      <c r="A15" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="44">
         <v>7.0</v>
       </c>
-      <c r="D15" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="42">
+      <c r="D15" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="45">
         <v>1.5</v>
       </c>
-      <c r="F15" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="G15" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="H15" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="I15" s="44">
+      <c r="F15" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="49">
         <v>1.5</v>
       </c>
-      <c r="J15" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="K15" s="38"/>
-      <c r="L15" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="M15" s="45">
+      <c r="J15" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" s="40"/>
+      <c r="L15" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="M15" s="50">
         <v>11.0</v>
       </c>
-      <c r="N15" s="42" t="s">
-        <v>34</v>
+      <c r="N15" s="45" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="36">
+      <c r="A16" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="37">
         <v>10.0</v>
       </c>
-      <c r="D16" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="37">
+      <c r="D16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="39">
         <v>1.5</v>
       </c>
-      <c r="F16" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I16" s="36">
+      <c r="F16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="37">
         <v>17.5</v>
       </c>
-      <c r="J16" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K16" s="38"/>
-      <c r="L16" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="M16" s="37">
+      <c r="J16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" s="40"/>
+      <c r="L16" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="M16" s="39">
         <v>29.0</v>
       </c>
-      <c r="N16" s="37">
+      <c r="N16" s="39">
         <v>50.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="41">
+      <c r="A17" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="44">
         <v>10.0</v>
       </c>
-      <c r="D17" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17" s="42">
+      <c r="D17" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="45">
         <v>1.5</v>
       </c>
-      <c r="F17" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="H17" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="I17" s="41">
+      <c r="F17" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="44">
         <v>25.0</v>
       </c>
-      <c r="J17" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="K17" s="38"/>
-      <c r="L17" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="M17" s="42">
+      <c r="J17" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" s="40"/>
+      <c r="L17" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="M17" s="45">
         <v>42.0</v>
       </c>
-      <c r="N17" s="42">
+      <c r="N17" s="45">
         <v>48.0</v>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="47"/>
+      <c r="J18" s="48"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -1528,19 +1528,19 @@
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>44736.0</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="7">
         <v>0.5111111111111111</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="7">
         <v>0.5666666666666667</v>
       </c>
       <c r="G3" s="2"/>
@@ -1555,8 +1555,8 @@
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>8</v>
+      <c r="B4" s="9" t="s">
+        <v>7</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -1572,7 +1572,7 @@
     </row>
     <row r="5">
       <c r="A5" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -1586,511 +1586,511 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
-      <c r="N5" s="11"/>
+      <c r="N5" s="12"/>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="s">
-        <v>10</v>
+      <c r="A6" s="17" t="s">
+        <v>11</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="D6" s="16"/>
+      <c r="E6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="F6" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="15"/>
-      <c r="I6" s="20" t="s">
+      <c r="G6" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="15"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="22" t="s">
+      <c r="H6" s="16"/>
+      <c r="I6" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="M6" s="23"/>
-      <c r="N6" s="15"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" s="24"/>
+      <c r="N6" s="16"/>
     </row>
     <row r="7">
-      <c r="A7" s="24"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="25" t="s">
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="D7" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="E7" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="28" t="s">
+      <c r="F7" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="G7" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="H7" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="J7" s="29" t="s">
+      <c r="I7" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="K7" s="30" t="s">
+      <c r="J7" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="L7" s="31" t="s">
+      <c r="K7" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="M7" s="30" t="s">
+      <c r="L7" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="N7" s="31" t="s">
+      <c r="M7" s="31" t="s">
         <v>30</v>
+      </c>
+      <c r="N7" s="32" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="35">
+      <c r="B8" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="38">
         <v>10.0</v>
       </c>
-      <c r="D8" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="37">
+      <c r="D8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="39">
         <v>1.5</v>
       </c>
-      <c r="F8" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I8" s="36">
+      <c r="F8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="37">
         <v>25.0</v>
       </c>
-      <c r="J8" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" s="37"/>
-      <c r="L8" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="M8" s="37">
+      <c r="J8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="39"/>
+      <c r="L8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="M8" s="39">
         <v>36.5</v>
       </c>
-      <c r="N8" s="37" t="s">
-        <v>34</v>
+      <c r="N8" s="39" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="40">
+        <v>33</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="43">
         <v>10.0</v>
       </c>
-      <c r="D9" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="42">
+      <c r="D9" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="45">
         <v>1.5</v>
       </c>
-      <c r="F9" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I9" s="41">
+      <c r="F9" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" s="44">
         <v>16.0</v>
       </c>
-      <c r="J9" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K9" s="37"/>
-      <c r="L9" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="M9" s="42">
+      <c r="J9" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="39"/>
+      <c r="L9" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9" s="45">
         <v>27.5</v>
       </c>
-      <c r="N9" s="37" t="s">
-        <v>34</v>
+      <c r="N9" s="39" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="35">
+        <v>33</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="38">
         <v>10.0</v>
       </c>
-      <c r="D10" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="37">
+      <c r="D10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="39">
         <v>1.5</v>
       </c>
-      <c r="F10" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I10" s="36">
+      <c r="F10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I10" s="37">
         <v>25.0</v>
       </c>
-      <c r="J10" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K10" s="37"/>
-      <c r="L10" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="M10" s="37">
+      <c r="J10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10" s="39">
         <v>36.5</v>
       </c>
-      <c r="N10" s="37" t="s">
-        <v>34</v>
+      <c r="N10" s="39" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="40">
+        <v>33</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="43">
         <v>10.0</v>
       </c>
-      <c r="D11" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="42">
+      <c r="D11" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="45">
         <v>1.5</v>
       </c>
-      <c r="F11" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I11" s="41">
+      <c r="F11" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="44">
         <v>25.0</v>
       </c>
-      <c r="J11" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K11" s="37"/>
-      <c r="L11" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="M11" s="37">
+      <c r="J11" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" s="39"/>
+      <c r="L11" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="M11" s="39">
         <v>36.5</v>
       </c>
-      <c r="N11" s="37" t="s">
-        <v>34</v>
+      <c r="N11" s="39" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="35">
+        <v>33</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="38">
         <v>10.0</v>
       </c>
-      <c r="D12" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="37">
+      <c r="D12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="39">
         <v>1.5</v>
       </c>
-      <c r="F12" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I12" s="36">
+      <c r="F12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="37">
         <v>25.0</v>
       </c>
-      <c r="J12" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K12" s="37"/>
-      <c r="L12" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="M12" s="37">
+      <c r="J12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" s="39"/>
+      <c r="L12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="M12" s="39">
         <v>36.5</v>
       </c>
-      <c r="N12" s="37" t="s">
-        <v>34</v>
+      <c r="N12" s="39" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="40">
+        <v>33</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="43">
         <v>10.0</v>
       </c>
-      <c r="D13" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="42">
+      <c r="D13" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="45">
         <v>1.5</v>
       </c>
-      <c r="F13" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H13" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I13" s="41">
+      <c r="F13" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="44">
         <v>25.0</v>
       </c>
-      <c r="J13" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K13" s="37"/>
-      <c r="L13" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="M13" s="37">
+      <c r="J13" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" s="39"/>
+      <c r="L13" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="M13" s="39">
         <v>36.5</v>
       </c>
-      <c r="N13" s="37" t="s">
-        <v>34</v>
+      <c r="N13" s="39" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="35">
+        <v>33</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="38">
         <v>10.0</v>
       </c>
-      <c r="D14" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="37">
+      <c r="D14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="39">
         <v>1.5</v>
       </c>
-      <c r="F14" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H14" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I14" s="36">
+      <c r="F14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" s="37">
         <v>25.0</v>
       </c>
-      <c r="J14" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K14" s="37"/>
-      <c r="L14" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="M14" s="37">
+      <c r="J14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="M14" s="39">
         <v>36.5</v>
       </c>
-      <c r="N14" s="37" t="s">
-        <v>34</v>
+      <c r="N14" s="39" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="40">
+        <v>33</v>
+      </c>
+      <c r="B15" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="43">
         <v>10.0</v>
       </c>
-      <c r="D15" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="42">
+      <c r="D15" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="45">
         <v>1.5</v>
       </c>
-      <c r="F15" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G15" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H15" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I15" s="41">
+      <c r="F15" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="44">
         <v>25.0</v>
       </c>
-      <c r="J15" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K15" s="37"/>
-      <c r="L15" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="M15" s="37">
+      <c r="J15" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="M15" s="39">
         <v>36.5</v>
       </c>
-      <c r="N15" s="37" t="s">
-        <v>34</v>
+      <c r="N15" s="39" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="35">
+        <v>33</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="38">
         <v>10.0</v>
       </c>
-      <c r="D16" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="37">
+      <c r="D16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="39">
         <v>1.5</v>
       </c>
-      <c r="F16" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I16" s="36">
+      <c r="F16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="37">
         <v>25.0</v>
       </c>
-      <c r="J16" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K16" s="37"/>
-      <c r="L16" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="M16" s="37">
+      <c r="J16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" s="39"/>
+      <c r="L16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="M16" s="39">
         <v>36.5</v>
       </c>
-      <c r="N16" s="37" t="s">
-        <v>34</v>
+      <c r="N16" s="39" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="40">
+        <v>33</v>
+      </c>
+      <c r="B17" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="43">
         <v>10.0</v>
       </c>
-      <c r="D17" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17" s="42">
+      <c r="D17" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="45">
         <v>1.5</v>
       </c>
-      <c r="F17" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H17" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I17" s="41">
+      <c r="F17" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="44">
         <v>25.0</v>
       </c>
-      <c r="J17" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K17" s="37"/>
-      <c r="L17" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="M17" s="37">
+      <c r="J17" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" s="39"/>
+      <c r="L17" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="M17" s="39">
         <v>36.5</v>
       </c>
-      <c r="N17" s="37" t="s">
-        <v>34</v>
+      <c r="N17" s="39" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="8"/>
+      <c r="D18" s="9"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="47"/>
+      <c r="J18" s="48"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -2170,19 +2170,19 @@
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>44736.0</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="7">
         <v>0.5104166666666666</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="7">
         <v>0.58125</v>
       </c>
       <c r="G3" s="2"/>
@@ -2197,8 +2197,8 @@
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>37</v>
+      <c r="B4" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -2214,7 +2214,7 @@
     </row>
     <row r="5">
       <c r="A5" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -2228,507 +2228,507 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
-      <c r="N5" s="11"/>
+      <c r="N5" s="12"/>
     </row>
     <row r="6">
-      <c r="A6" s="43" t="s">
-        <v>10</v>
+      <c r="A6" s="15" t="s">
+        <v>11</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="D6" s="16"/>
+      <c r="E6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="F6" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="15"/>
-      <c r="I6" s="20" t="s">
+      <c r="G6" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="15"/>
-      <c r="K6" s="22" t="s">
+      <c r="H6" s="16"/>
+      <c r="I6" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="15"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="16"/>
     </row>
     <row r="7">
-      <c r="A7" s="24"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="25" t="s">
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="D7" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="E7" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="28" t="s">
+      <c r="F7" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="G7" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="H7" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="J7" s="29" t="s">
+      <c r="I7" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="K7" s="30" t="s">
+      <c r="J7" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="L7" s="30" t="s">
+      <c r="K7" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="M7" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="N7" s="31" t="s">
-        <v>30</v>
+      <c r="L7" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" s="32" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="36">
+      <c r="A8" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="37">
         <v>10.0</v>
       </c>
-      <c r="D8" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="37">
+      <c r="D8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="39">
         <v>1.5</v>
       </c>
-      <c r="F8" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I8" s="36">
+      <c r="F8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="37">
         <v>25.0</v>
       </c>
-      <c r="J8" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" s="48">
+      <c r="J8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="41">
         <v>0.5111111111111111</v>
       </c>
-      <c r="L8" s="37"/>
-      <c r="M8" s="37">
+      <c r="L8" s="39"/>
+      <c r="M8" s="39">
         <f>58+56+23</f>
         <v>137</v>
       </c>
-      <c r="N8" s="37">
+      <c r="N8" s="39">
         <v>50.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="36">
+      <c r="A9" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="37">
         <v>10.0</v>
       </c>
-      <c r="D9" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="37">
+      <c r="D9" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="39">
         <v>1.5</v>
       </c>
-      <c r="F9" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I9" s="36">
+      <c r="F9" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" s="37">
         <v>25.0</v>
       </c>
-      <c r="J9" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K9" s="49">
+      <c r="J9" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="46">
         <v>0.51875</v>
       </c>
-      <c r="L9" s="42"/>
-      <c r="M9" s="42">
+      <c r="L9" s="45"/>
+      <c r="M9" s="45">
         <f>50+52+32</f>
         <v>134</v>
       </c>
-      <c r="N9" s="42">
+      <c r="N9" s="45">
         <v>47.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="36">
+      <c r="A10" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="37">
         <v>10.0</v>
       </c>
-      <c r="D10" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="37">
+      <c r="D10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="39">
         <v>1.5</v>
       </c>
-      <c r="F10" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I10" s="36">
+      <c r="F10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I10" s="37">
         <v>25.0</v>
       </c>
-      <c r="J10" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K10" s="48">
+      <c r="J10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" s="41">
         <v>0.5277777777777778</v>
       </c>
-      <c r="L10" s="37"/>
-      <c r="M10" s="37">
+      <c r="L10" s="39"/>
+      <c r="M10" s="39">
         <f>56+19</f>
         <v>75</v>
       </c>
-      <c r="N10" s="37">
+      <c r="N10" s="39">
         <v>47.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="36">
+      <c r="A11" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="37">
         <v>10.0</v>
       </c>
-      <c r="D11" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="37">
+      <c r="D11" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="39">
         <v>1.5</v>
       </c>
-      <c r="F11" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I11" s="36">
+      <c r="F11" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="37">
         <v>25.0</v>
       </c>
-      <c r="J11" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K11" s="49">
+      <c r="J11" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" s="46">
         <v>0.5340277777777778</v>
       </c>
-      <c r="L11" s="42"/>
-      <c r="M11" s="42">
+      <c r="L11" s="45"/>
+      <c r="M11" s="45">
         <f>53+52</f>
         <v>105</v>
       </c>
-      <c r="N11" s="42">
+      <c r="N11" s="45">
         <v>48.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="36">
+      <c r="A12" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="37">
         <v>10.0</v>
       </c>
-      <c r="D12" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="37">
+      <c r="D12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="39">
         <v>1.5</v>
       </c>
-      <c r="F12" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I12" s="36">
+      <c r="F12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="37">
         <v>25.0</v>
       </c>
-      <c r="J12" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K12" s="48">
+      <c r="J12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" s="41">
         <v>0.5416666666666666</v>
       </c>
-      <c r="L12" s="37"/>
-      <c r="M12" s="37">
+      <c r="L12" s="39"/>
+      <c r="M12" s="39">
         <f>59+50+1</f>
         <v>110</v>
       </c>
-      <c r="N12" s="37">
+      <c r="N12" s="39">
         <v>50.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="36">
+      <c r="A13" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="37">
         <v>10.0</v>
       </c>
-      <c r="D13" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="37">
+      <c r="D13" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="39">
         <v>1.5</v>
       </c>
-      <c r="F13" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H13" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I13" s="36">
+      <c r="F13" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="37">
         <v>25.0</v>
       </c>
-      <c r="J13" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K13" s="49">
+      <c r="J13" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" s="46">
         <v>0.5486111111111112</v>
       </c>
-      <c r="L13" s="42"/>
-      <c r="M13" s="50">
+      <c r="L13" s="45"/>
+      <c r="M13" s="47">
         <f>53+55+20</f>
         <v>128</v>
       </c>
-      <c r="N13" s="42">
+      <c r="N13" s="45">
         <v>50.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="36">
+      <c r="A14" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="37">
         <v>10.0</v>
       </c>
-      <c r="D14" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="37">
+      <c r="D14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="39">
         <v>1.5</v>
       </c>
-      <c r="F14" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H14" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I14" s="36">
+      <c r="F14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" s="37">
         <v>25.0</v>
       </c>
-      <c r="J14" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K14" s="48">
+      <c r="J14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="41">
         <v>0.5555555555555556</v>
       </c>
-      <c r="L14" s="37"/>
-      <c r="M14" s="37">
+      <c r="L14" s="39"/>
+      <c r="M14" s="39">
         <f>55+51</f>
         <v>106</v>
       </c>
-      <c r="N14" s="37">
+      <c r="N14" s="39">
         <v>47.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="36">
+      <c r="A15" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="37">
         <v>10.0</v>
       </c>
-      <c r="D15" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="37">
+      <c r="D15" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="39">
         <v>1.5</v>
       </c>
-      <c r="F15" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G15" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H15" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I15" s="36">
+      <c r="F15" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="37">
         <v>25.0</v>
       </c>
-      <c r="J15" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K15" s="49">
+      <c r="J15" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" s="46">
         <v>0.5625</v>
       </c>
-      <c r="L15" s="42"/>
-      <c r="M15" s="42">
+      <c r="L15" s="45"/>
+      <c r="M15" s="45">
         <f>56+52+14</f>
         <v>122</v>
       </c>
-      <c r="N15" s="42">
+      <c r="N15" s="45">
         <v>49.0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="36">
+      <c r="A16" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="37">
         <v>10.0</v>
       </c>
-      <c r="D16" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="37">
+      <c r="D16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="39">
         <v>1.5</v>
       </c>
-      <c r="F16" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I16" s="36">
+      <c r="F16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="37">
         <v>25.0</v>
       </c>
-      <c r="J16" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K16" s="48">
+      <c r="J16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" s="41">
         <v>0.5694444444444444</v>
       </c>
-      <c r="L16" s="37"/>
-      <c r="M16" s="37">
+      <c r="L16" s="39"/>
+      <c r="M16" s="39">
         <f>55+37</f>
         <v>92</v>
       </c>
-      <c r="N16" s="37">
+      <c r="N16" s="39">
         <v>50.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="46" t="s">
+      <c r="A17" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="36">
+      <c r="C17" s="37">
         <v>10.0</v>
       </c>
-      <c r="D17" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17" s="37">
+      <c r="D17" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="39">
         <v>1.5</v>
       </c>
-      <c r="F17" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="H17" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="I17" s="36">
+      <c r="F17" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="37">
         <v>25.0</v>
       </c>
-      <c r="J17" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="K17" s="49">
+      <c r="J17" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" s="46">
         <v>0.5770833333333333</v>
       </c>
-      <c r="L17" s="42"/>
-      <c r="M17" s="42">
+      <c r="L17" s="45"/>
+      <c r="M17" s="45">
         <f>56+41+30</f>
         <v>127</v>
       </c>
-      <c r="N17" s="42">
+      <c r="N17" s="45">
         <v>46.0</v>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="47"/>
+      <c r="J18" s="48"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>

--- a/processing_scripts/Inventory_Processing/2022 Metadata Creation/T4 TMP Data Sheet.xlsx
+++ b/processing_scripts/Inventory_Processing/2022 Metadata Creation/T4 TMP Data Sheet.xlsx
@@ -30,24 +30,24 @@
     <t>End:</t>
   </si>
   <si>
+    <t>Personnel:</t>
+  </si>
+  <si>
+    <t>AES</t>
+  </si>
+  <si>
+    <t>MKB</t>
+  </si>
+  <si>
     <t>NA</t>
   </si>
   <si>
-    <t>Personnel:</t>
-  </si>
-  <si>
-    <t>AES</t>
+    <t>Depth: 15cm</t>
   </si>
   <si>
     <t>EP</t>
   </si>
   <si>
-    <t>MKB</t>
-  </si>
-  <si>
-    <t>Depth: 15cm</t>
-  </si>
-  <si>
     <t>Plot</t>
   </si>
   <si>
@@ -105,25 +105,25 @@
     <t>Total Volume</t>
   </si>
   <si>
+    <t>Evacuated (cb)</t>
+  </si>
+  <si>
+    <t>SEAWATER</t>
+  </si>
+  <si>
+    <t>Total volume</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROL </t>
+  </si>
+  <si>
     <t>Total Vol</t>
   </si>
   <si>
-    <t>Total volume</t>
-  </si>
-  <si>
-    <t>Evacuated (cb)</t>
-  </si>
-  <si>
     <t>FRESHWATER</t>
-  </si>
-  <si>
-    <t>SEAWATER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROL </t>
-  </si>
-  <si>
-    <t>C3</t>
   </si>
   <si>
     <t>—</t>
@@ -199,14 +199,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00DA63"/>
-        <bgColor rgb="FF00DA63"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5E2FD"/>
-        <bgColor rgb="FFA5E2FD"/>
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
       </patternFill>
     </fill>
     <fill>
@@ -217,8 +211,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor theme="4"/>
+        <fgColor rgb="FF00DA63"/>
+        <bgColor rgb="FF00DA63"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5E2FD"/>
+        <bgColor rgb="FFA5E2FD"/>
       </patternFill>
     </fill>
     <fill>
@@ -358,23 +358,23 @@
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="3" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
-    </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
-    </xf>
     <xf borderId="1" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
@@ -395,7 +395,7 @@
     </xf>
     <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -416,33 +416,33 @@
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
@@ -450,24 +450,24 @@
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -506,11 +506,11 @@
       <tableStyleElement dxfId="1" type="firstRowStripe"/>
       <tableStyleElement dxfId="2" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="2" pivot="0" name="SEAWATER-style">
+    <tableStyle count="2" pivot="0" name="FRESHWATER-style">
       <tableStyleElement dxfId="1" type="firstRowStripe"/>
       <tableStyleElement dxfId="2" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="2" pivot="0" name="FRESHWATER-style">
+    <tableStyle count="2" pivot="0" name="SEAWATER-style">
       <tableStyleElement dxfId="1" type="firstRowStripe"/>
       <tableStyleElement dxfId="2" type="secondRowStripe"/>
     </tableStyle>
@@ -555,7 +555,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D8:N17" displayName="Table_2" name="Table_2" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D8:N17" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="11">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -574,7 +574,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C8:N17" displayName="Table_3" name="Table_3" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C8:N17" displayName="Table_3" name="Table_3" id="3">
   <tableColumns count="12">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -847,7 +847,7 @@
         <v>4</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -860,10 +860,10 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -880,7 +880,7 @@
     </row>
     <row r="5">
       <c r="A5" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -897,16 +897,16 @@
       <c r="N5" s="3"/>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="E6" s="18" t="s">
         <v>14</v>
       </c>
@@ -916,17 +916,17 @@
       <c r="G6" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="16"/>
+      <c r="H6" s="17"/>
       <c r="I6" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="16"/>
+      <c r="J6" s="17"/>
       <c r="K6" s="22"/>
       <c r="L6" s="23" t="s">
         <v>18</v>
       </c>
       <c r="M6" s="24"/>
-      <c r="N6" s="16"/>
+      <c r="N6" s="17"/>
     </row>
     <row r="7">
       <c r="A7" s="25"/>
@@ -962,429 +962,429 @@
         <v>28</v>
       </c>
       <c r="M7" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N7" s="32" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>36</v>
+      <c r="A8" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>33</v>
       </c>
       <c r="C8" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" s="39" t="s">
+      <c r="D8" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="38" t="s">
         <v>37</v>
       </c>
       <c r="I8" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="J8" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="K8" s="40"/>
-      <c r="L8" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="M8" s="39">
+      <c r="J8" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="M8" s="38">
         <v>0.0</v>
       </c>
-      <c r="N8" s="39" t="s">
+      <c r="N8" s="38" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="s">
-        <v>35</v>
+      <c r="A9" s="35" t="s">
+        <v>34</v>
       </c>
       <c r="B9" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="I9" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="J9" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="K9" s="40"/>
-      <c r="L9" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="M9" s="45">
+      <c r="C9" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="41"/>
+      <c r="L9" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9" s="44">
         <v>0.0</v>
       </c>
-      <c r="N9" s="45" t="s">
+      <c r="N9" s="44" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="35" t="s">
+      <c r="A10" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="34" t="s">
         <v>39</v>
       </c>
       <c r="C10" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" s="39" t="s">
+      <c r="D10" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="38" t="s">
         <v>37</v>
       </c>
       <c r="I10" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="J10" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="M10" s="39" t="s">
-        <v>5</v>
-      </c>
-      <c r="N10" s="39" t="s">
+      <c r="J10" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="38" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="s">
-        <v>35</v>
+      <c r="A11" s="35" t="s">
+        <v>34</v>
       </c>
       <c r="B11" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="44">
+      <c r="C11" s="43">
         <v>10.0</v>
       </c>
-      <c r="D11" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="45">
+      <c r="D11" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="44">
         <v>1.5</v>
       </c>
-      <c r="F11" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="H11" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="I11" s="44">
+      <c r="F11" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="43">
         <v>12.5</v>
       </c>
-      <c r="J11" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="K11" s="40"/>
-      <c r="L11" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="M11" s="45">
+      <c r="J11" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="M11" s="44">
         <v>24.0</v>
       </c>
-      <c r="N11" s="45">
+      <c r="N11" s="44">
         <v>50.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="35" t="s">
+      <c r="A12" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="34" t="s">
         <v>41</v>
       </c>
       <c r="C12" s="37">
         <v>10.0</v>
       </c>
-      <c r="D12" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="39">
+      <c r="D12" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="38">
         <v>1.5</v>
       </c>
-      <c r="F12" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H12" s="39" t="s">
+      <c r="F12" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="38" t="s">
         <v>37</v>
       </c>
       <c r="I12" s="37">
         <v>25.0</v>
       </c>
-      <c r="J12" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="K12" s="40"/>
-      <c r="L12" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="M12" s="39">
+      <c r="J12" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="M12" s="38">
         <v>40.0</v>
       </c>
-      <c r="N12" s="39">
+      <c r="N12" s="38">
         <v>50.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="s">
-        <v>35</v>
+      <c r="A13" s="35" t="s">
+        <v>34</v>
       </c>
       <c r="B13" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="I13" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="J13" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="K13" s="40"/>
-      <c r="L13" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="M13" s="45">
+      <c r="C13" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" s="41"/>
+      <c r="L13" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="M13" s="44">
         <v>0.0</v>
       </c>
-      <c r="N13" s="45" t="s">
+      <c r="N13" s="44" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="35" t="s">
+      <c r="A14" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="34" t="s">
         <v>43</v>
       </c>
       <c r="C14" s="37">
         <v>10.0</v>
       </c>
-      <c r="D14" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="39">
+      <c r="D14" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="38">
         <v>1.5</v>
       </c>
-      <c r="F14" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G14" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H14" s="39" t="s">
+      <c r="F14" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="38" t="s">
         <v>37</v>
       </c>
       <c r="I14" s="37">
         <v>25.0</v>
       </c>
-      <c r="J14" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="K14" s="40"/>
-      <c r="L14" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="M14" s="39">
+      <c r="J14" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="M14" s="38">
         <v>42.0</v>
       </c>
-      <c r="N14" s="39">
+      <c r="N14" s="38">
         <v>50.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="s">
-        <v>35</v>
+      <c r="A15" s="35" t="s">
+        <v>34</v>
       </c>
       <c r="B15" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="44">
+      <c r="C15" s="43">
         <v>7.0</v>
       </c>
-      <c r="D15" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" s="45">
+      <c r="D15" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="44">
         <v>1.5</v>
       </c>
-      <c r="F15" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="G15" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="H15" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="I15" s="49">
+      <c r="F15" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="47">
         <v>1.5</v>
       </c>
-      <c r="J15" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="K15" s="40"/>
-      <c r="L15" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="M15" s="50">
+      <c r="J15" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="M15" s="49">
         <v>11.0</v>
       </c>
-      <c r="N15" s="45" t="s">
+      <c r="N15" s="44" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="35" t="s">
+      <c r="A16" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="34" t="s">
         <v>45</v>
       </c>
       <c r="C16" s="37">
         <v>10.0</v>
       </c>
-      <c r="D16" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" s="39">
+      <c r="D16" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="38">
         <v>1.5</v>
       </c>
-      <c r="F16" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G16" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H16" s="39" t="s">
+      <c r="F16" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="38" t="s">
         <v>37</v>
       </c>
       <c r="I16" s="37">
         <v>17.5</v>
       </c>
-      <c r="J16" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="K16" s="40"/>
-      <c r="L16" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="M16" s="39">
+      <c r="J16" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="M16" s="38">
         <v>29.0</v>
       </c>
-      <c r="N16" s="39">
+      <c r="N16" s="38">
         <v>50.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="s">
-        <v>35</v>
+      <c r="A17" s="35" t="s">
+        <v>34</v>
       </c>
       <c r="B17" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="44">
+      <c r="C17" s="43">
         <v>10.0</v>
       </c>
-      <c r="D17" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="E17" s="45">
+      <c r="D17" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="44">
         <v>1.5</v>
       </c>
-      <c r="F17" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="G17" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="H17" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="I17" s="44">
+      <c r="F17" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="43">
         <v>25.0</v>
       </c>
-      <c r="J17" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="K17" s="40"/>
-      <c r="L17" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="M17" s="45">
+      <c r="J17" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="M17" s="44">
         <v>42.0</v>
       </c>
-      <c r="N17" s="45">
+      <c r="N17" s="44">
         <v>48.0</v>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="48"/>
+      <c r="J18" s="50"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>7</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -1572,7 +1572,7 @@
     </row>
     <row r="5">
       <c r="A5" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -1586,19 +1586,19 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
-      <c r="N5" s="12"/>
+      <c r="N5" s="11"/>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="E6" s="18" t="s">
         <v>14</v>
       </c>
@@ -1608,17 +1608,17 @@
       <c r="G6" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="16"/>
+      <c r="H6" s="17"/>
       <c r="I6" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="16"/>
+      <c r="J6" s="17"/>
       <c r="K6" s="22"/>
       <c r="L6" s="23" t="s">
         <v>18</v>
       </c>
       <c r="M6" s="24"/>
-      <c r="N6" s="16"/>
+      <c r="N6" s="17"/>
     </row>
     <row r="7">
       <c r="A7" s="25"/>
@@ -1654,429 +1654,429 @@
         <v>28</v>
       </c>
       <c r="M7" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="N7" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="N7" s="32" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="38">
+      <c r="C8" s="39">
         <v>10.0</v>
       </c>
-      <c r="D8" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="39">
+      <c r="D8" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="38">
         <v>1.5</v>
       </c>
-      <c r="F8" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" s="39" t="s">
+      <c r="F8" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="38" t="s">
         <v>37</v>
       </c>
       <c r="I8" s="37">
         <v>25.0</v>
       </c>
-      <c r="J8" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="K8" s="39"/>
-      <c r="L8" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="M8" s="39">
+      <c r="J8" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="38"/>
+      <c r="L8" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="M8" s="38">
         <v>36.5</v>
       </c>
-      <c r="N8" s="39" t="s">
+      <c r="N8" s="38" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="s">
-        <v>33</v>
+      <c r="A9" s="36" t="s">
+        <v>36</v>
       </c>
       <c r="B9" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="43">
+      <c r="C9" s="45">
         <v>10.0</v>
       </c>
-      <c r="D9" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="45">
+      <c r="D9" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="44">
         <v>1.5</v>
       </c>
-      <c r="F9" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="I9" s="44">
+      <c r="F9" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" s="43">
         <v>16.0</v>
       </c>
-      <c r="J9" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="K9" s="39"/>
-      <c r="L9" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="M9" s="45">
+      <c r="J9" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="38"/>
+      <c r="L9" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9" s="44">
         <v>27.5</v>
       </c>
-      <c r="N9" s="39" t="s">
+      <c r="N9" s="38" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="35" t="s">
+      <c r="A10" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="38">
+      <c r="C10" s="39">
         <v>10.0</v>
       </c>
-      <c r="D10" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="39">
+      <c r="D10" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="38">
         <v>1.5</v>
       </c>
-      <c r="F10" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" s="39" t="s">
+      <c r="F10" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="38" t="s">
         <v>37</v>
       </c>
       <c r="I10" s="37">
         <v>25.0</v>
       </c>
-      <c r="J10" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="K10" s="39"/>
-      <c r="L10" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="M10" s="39">
+      <c r="J10" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10" s="38">
         <v>36.5</v>
       </c>
-      <c r="N10" s="39" t="s">
+      <c r="N10" s="38" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="s">
-        <v>33</v>
+      <c r="A11" s="36" t="s">
+        <v>36</v>
       </c>
       <c r="B11" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="43">
+      <c r="C11" s="45">
         <v>10.0</v>
       </c>
-      <c r="D11" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="45">
+      <c r="D11" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="44">
         <v>1.5</v>
       </c>
-      <c r="F11" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H11" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="I11" s="44">
+      <c r="F11" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="43">
         <v>25.0</v>
       </c>
-      <c r="J11" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="M11" s="39">
+      <c r="J11" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="M11" s="38">
         <v>36.5</v>
       </c>
-      <c r="N11" s="39" t="s">
+      <c r="N11" s="38" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="35" t="s">
+      <c r="A12" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="38">
+      <c r="C12" s="39">
         <v>10.0</v>
       </c>
-      <c r="D12" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="39">
+      <c r="D12" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="38">
         <v>1.5</v>
       </c>
-      <c r="F12" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H12" s="39" t="s">
+      <c r="F12" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="38" t="s">
         <v>37</v>
       </c>
       <c r="I12" s="37">
         <v>25.0</v>
       </c>
-      <c r="J12" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="M12" s="39">
+      <c r="J12" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" s="38"/>
+      <c r="L12" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="M12" s="38">
         <v>36.5</v>
       </c>
-      <c r="N12" s="39" t="s">
+      <c r="N12" s="38" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="s">
-        <v>33</v>
+      <c r="A13" s="36" t="s">
+        <v>36</v>
       </c>
       <c r="B13" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="43">
+      <c r="C13" s="45">
         <v>10.0</v>
       </c>
-      <c r="D13" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="45">
+      <c r="D13" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="44">
         <v>1.5</v>
       </c>
-      <c r="F13" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="I13" s="44">
+      <c r="F13" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="43">
         <v>25.0</v>
       </c>
-      <c r="J13" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="K13" s="39"/>
-      <c r="L13" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="M13" s="39">
+      <c r="J13" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" s="38"/>
+      <c r="L13" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="M13" s="38">
         <v>36.5</v>
       </c>
-      <c r="N13" s="39" t="s">
+      <c r="N13" s="38" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="35" t="s">
+      <c r="A14" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="38">
+      <c r="C14" s="39">
         <v>10.0</v>
       </c>
-      <c r="D14" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="39">
+      <c r="D14" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="38">
         <v>1.5</v>
       </c>
-      <c r="F14" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G14" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H14" s="39" t="s">
+      <c r="F14" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="38" t="s">
         <v>37</v>
       </c>
       <c r="I14" s="37">
         <v>25.0</v>
       </c>
-      <c r="J14" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="K14" s="39"/>
-      <c r="L14" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="M14" s="39">
+      <c r="J14" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="38"/>
+      <c r="L14" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="M14" s="38">
         <v>36.5</v>
       </c>
-      <c r="N14" s="39" t="s">
+      <c r="N14" s="38" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="33" t="s">
-        <v>33</v>
+      <c r="A15" s="36" t="s">
+        <v>36</v>
       </c>
       <c r="B15" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="43">
+      <c r="C15" s="45">
         <v>10.0</v>
       </c>
-      <c r="D15" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" s="45">
+      <c r="D15" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="44">
         <v>1.5</v>
       </c>
-      <c r="F15" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G15" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H15" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="I15" s="44">
+      <c r="F15" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="43">
         <v>25.0</v>
       </c>
-      <c r="J15" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="K15" s="39"/>
-      <c r="L15" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="M15" s="39">
+      <c r="J15" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" s="38"/>
+      <c r="L15" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="M15" s="38">
         <v>36.5</v>
       </c>
-      <c r="N15" s="39" t="s">
+      <c r="N15" s="38" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="35" t="s">
+      <c r="A16" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="38">
+      <c r="C16" s="39">
         <v>10.0</v>
       </c>
-      <c r="D16" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" s="39">
+      <c r="D16" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="38">
         <v>1.5</v>
       </c>
-      <c r="F16" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G16" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H16" s="39" t="s">
+      <c r="F16" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="38" t="s">
         <v>37</v>
       </c>
       <c r="I16" s="37">
         <v>25.0</v>
       </c>
-      <c r="J16" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="K16" s="39"/>
-      <c r="L16" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="M16" s="39">
+      <c r="J16" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" s="38"/>
+      <c r="L16" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="M16" s="38">
         <v>36.5</v>
       </c>
-      <c r="N16" s="39" t="s">
+      <c r="N16" s="38" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="s">
-        <v>33</v>
+      <c r="A17" s="36" t="s">
+        <v>36</v>
       </c>
       <c r="B17" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="43">
+      <c r="C17" s="45">
         <v>10.0</v>
       </c>
-      <c r="D17" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E17" s="45">
+      <c r="D17" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="44">
         <v>1.5</v>
       </c>
-      <c r="F17" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G17" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H17" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="I17" s="44">
+      <c r="F17" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="43">
         <v>25.0</v>
       </c>
-      <c r="J17" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="K17" s="39"/>
-      <c r="L17" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="M17" s="39">
+      <c r="J17" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" s="38"/>
+      <c r="L17" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="M17" s="38">
         <v>36.5</v>
       </c>
-      <c r="N17" s="39" t="s">
+      <c r="N17" s="38" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="48"/>
+      <c r="J18" s="50"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -2214,7 +2214,7 @@
     </row>
     <row r="5">
       <c r="A5" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -2228,19 +2228,19 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
-      <c r="N5" s="12"/>
+      <c r="N5" s="11"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="E6" s="18" t="s">
         <v>14</v>
       </c>
@@ -2250,17 +2250,17 @@
       <c r="G6" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="16"/>
+      <c r="H6" s="17"/>
       <c r="I6" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="16"/>
+      <c r="J6" s="17"/>
       <c r="K6" s="23" t="s">
         <v>18</v>
       </c>
       <c r="L6" s="24"/>
       <c r="M6" s="24"/>
-      <c r="N6" s="16"/>
+      <c r="N6" s="17"/>
     </row>
     <row r="7">
       <c r="A7" s="25"/>
@@ -2299,55 +2299,55 @@
         <v>29</v>
       </c>
       <c r="N7" s="32" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>36</v>
+      <c r="A8" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>33</v>
       </c>
       <c r="C8" s="37">
         <v>10.0</v>
       </c>
-      <c r="D8" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="39">
+      <c r="D8" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="38">
         <v>1.5</v>
       </c>
-      <c r="F8" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" s="39" t="s">
+      <c r="F8" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="38" t="s">
         <v>37</v>
       </c>
       <c r="I8" s="37">
         <v>25.0</v>
       </c>
-      <c r="J8" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="K8" s="41">
+      <c r="J8" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="40">
         <v>0.5111111111111111</v>
       </c>
-      <c r="L8" s="39"/>
-      <c r="M8" s="39">
+      <c r="L8" s="38"/>
+      <c r="M8" s="38">
         <f>58+56+23</f>
         <v>137</v>
       </c>
-      <c r="N8" s="39">
+      <c r="N8" s="38">
         <v>50.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="s">
-        <v>34</v>
+      <c r="A9" s="33" t="s">
+        <v>31</v>
       </c>
       <c r="B9" s="42" t="s">
         <v>38</v>
@@ -2355,85 +2355,85 @@
       <c r="C9" s="37">
         <v>10.0</v>
       </c>
-      <c r="D9" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="39">
+      <c r="D9" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="38">
         <v>1.5</v>
       </c>
-      <c r="F9" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" s="39" t="s">
+      <c r="F9" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="38" t="s">
         <v>37</v>
       </c>
       <c r="I9" s="37">
         <v>25.0</v>
       </c>
-      <c r="J9" s="39" t="s">
+      <c r="J9" s="38" t="s">
         <v>37</v>
       </c>
       <c r="K9" s="46">
         <v>0.51875</v>
       </c>
-      <c r="L9" s="45"/>
-      <c r="M9" s="45">
+      <c r="L9" s="44"/>
+      <c r="M9" s="44">
         <f>50+52+32</f>
         <v>134</v>
       </c>
-      <c r="N9" s="45">
+      <c r="N9" s="44">
         <v>47.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="35" t="s">
+      <c r="A10" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="34" t="s">
         <v>39</v>
       </c>
       <c r="C10" s="37">
         <v>10.0</v>
       </c>
-      <c r="D10" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="39">
+      <c r="D10" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="38">
         <v>1.5</v>
       </c>
-      <c r="F10" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" s="39" t="s">
+      <c r="F10" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="38" t="s">
         <v>37</v>
       </c>
       <c r="I10" s="37">
         <v>25.0</v>
       </c>
-      <c r="J10" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="K10" s="41">
+      <c r="J10" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" s="40">
         <v>0.5277777777777778</v>
       </c>
-      <c r="L10" s="39"/>
-      <c r="M10" s="39">
+      <c r="L10" s="38"/>
+      <c r="M10" s="38">
         <f>56+19</f>
         <v>75</v>
       </c>
-      <c r="N10" s="39">
+      <c r="N10" s="38">
         <v>47.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="s">
-        <v>34</v>
+      <c r="A11" s="33" t="s">
+        <v>31</v>
       </c>
       <c r="B11" s="42" t="s">
         <v>40</v>
@@ -2441,85 +2441,85 @@
       <c r="C11" s="37">
         <v>10.0</v>
       </c>
-      <c r="D11" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="39">
+      <c r="D11" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="38">
         <v>1.5</v>
       </c>
-      <c r="F11" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H11" s="39" t="s">
+      <c r="F11" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="38" t="s">
         <v>37</v>
       </c>
       <c r="I11" s="37">
         <v>25.0</v>
       </c>
-      <c r="J11" s="39" t="s">
+      <c r="J11" s="38" t="s">
         <v>37</v>
       </c>
       <c r="K11" s="46">
         <v>0.5340277777777778</v>
       </c>
-      <c r="L11" s="45"/>
-      <c r="M11" s="45">
+      <c r="L11" s="44"/>
+      <c r="M11" s="44">
         <f>53+52</f>
         <v>105</v>
       </c>
-      <c r="N11" s="45">
+      <c r="N11" s="44">
         <v>48.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="35" t="s">
+      <c r="A12" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="34" t="s">
         <v>41</v>
       </c>
       <c r="C12" s="37">
         <v>10.0</v>
       </c>
-      <c r="D12" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="39">
+      <c r="D12" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="38">
         <v>1.5</v>
       </c>
-      <c r="F12" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H12" s="39" t="s">
+      <c r="F12" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="38" t="s">
         <v>37</v>
       </c>
       <c r="I12" s="37">
         <v>25.0</v>
       </c>
-      <c r="J12" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="K12" s="41">
+      <c r="J12" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" s="40">
         <v>0.5416666666666666</v>
       </c>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39">
+      <c r="L12" s="38"/>
+      <c r="M12" s="38">
         <f>59+50+1</f>
         <v>110</v>
       </c>
-      <c r="N12" s="39">
+      <c r="N12" s="38">
         <v>50.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="s">
-        <v>34</v>
+      <c r="A13" s="33" t="s">
+        <v>31</v>
       </c>
       <c r="B13" s="42" t="s">
         <v>42</v>
@@ -2527,85 +2527,85 @@
       <c r="C13" s="37">
         <v>10.0</v>
       </c>
-      <c r="D13" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="39">
+      <c r="D13" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="38">
         <v>1.5</v>
       </c>
-      <c r="F13" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" s="39" t="s">
+      <c r="F13" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="38" t="s">
         <v>37</v>
       </c>
       <c r="I13" s="37">
         <v>25.0</v>
       </c>
-      <c r="J13" s="39" t="s">
+      <c r="J13" s="38" t="s">
         <v>37</v>
       </c>
       <c r="K13" s="46">
         <v>0.5486111111111112</v>
       </c>
-      <c r="L13" s="45"/>
-      <c r="M13" s="47">
+      <c r="L13" s="44"/>
+      <c r="M13" s="48">
         <f>53+55+20</f>
         <v>128</v>
       </c>
-      <c r="N13" s="45">
+      <c r="N13" s="44">
         <v>50.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="35" t="s">
+      <c r="A14" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="34" t="s">
         <v>43</v>
       </c>
       <c r="C14" s="37">
         <v>10.0</v>
       </c>
-      <c r="D14" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="39">
+      <c r="D14" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="38">
         <v>1.5</v>
       </c>
-      <c r="F14" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G14" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H14" s="39" t="s">
+      <c r="F14" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="38" t="s">
         <v>37</v>
       </c>
       <c r="I14" s="37">
         <v>25.0</v>
       </c>
-      <c r="J14" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="K14" s="41">
+      <c r="J14" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="40">
         <v>0.5555555555555556</v>
       </c>
-      <c r="L14" s="39"/>
-      <c r="M14" s="39">
+      <c r="L14" s="38"/>
+      <c r="M14" s="38">
         <f>55+51</f>
         <v>106</v>
       </c>
-      <c r="N14" s="39">
+      <c r="N14" s="38">
         <v>47.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="s">
-        <v>34</v>
+      <c r="A15" s="33" t="s">
+        <v>31</v>
       </c>
       <c r="B15" s="42" t="s">
         <v>44</v>
@@ -2613,85 +2613,85 @@
       <c r="C15" s="37">
         <v>10.0</v>
       </c>
-      <c r="D15" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" s="39">
+      <c r="D15" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="38">
         <v>1.5</v>
       </c>
-      <c r="F15" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G15" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H15" s="39" t="s">
+      <c r="F15" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="38" t="s">
         <v>37</v>
       </c>
       <c r="I15" s="37">
         <v>25.0</v>
       </c>
-      <c r="J15" s="39" t="s">
+      <c r="J15" s="38" t="s">
         <v>37</v>
       </c>
       <c r="K15" s="46">
         <v>0.5625</v>
       </c>
-      <c r="L15" s="45"/>
-      <c r="M15" s="45">
+      <c r="L15" s="44"/>
+      <c r="M15" s="44">
         <f>56+52+14</f>
         <v>122</v>
       </c>
-      <c r="N15" s="45">
+      <c r="N15" s="44">
         <v>49.0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="35" t="s">
+      <c r="A16" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="34" t="s">
         <v>45</v>
       </c>
       <c r="C16" s="37">
         <v>10.0</v>
       </c>
-      <c r="D16" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" s="39">
+      <c r="D16" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="38">
         <v>1.5</v>
       </c>
-      <c r="F16" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G16" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H16" s="39" t="s">
+      <c r="F16" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="38" t="s">
         <v>37</v>
       </c>
       <c r="I16" s="37">
         <v>25.0</v>
       </c>
-      <c r="J16" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="K16" s="41">
+      <c r="J16" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" s="40">
         <v>0.5694444444444444</v>
       </c>
-      <c r="L16" s="39"/>
-      <c r="M16" s="39">
+      <c r="L16" s="38"/>
+      <c r="M16" s="38">
         <f>55+37</f>
         <v>92</v>
       </c>
-      <c r="N16" s="39">
+      <c r="N16" s="38">
         <v>50.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="s">
-        <v>34</v>
+      <c r="A17" s="33" t="s">
+        <v>31</v>
       </c>
       <c r="B17" s="42" t="s">
         <v>46</v>
@@ -2699,36 +2699,36 @@
       <c r="C17" s="37">
         <v>10.0</v>
       </c>
-      <c r="D17" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E17" s="39">
+      <c r="D17" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="38">
         <v>1.5</v>
       </c>
-      <c r="F17" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G17" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H17" s="39" t="s">
+      <c r="F17" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="38" t="s">
         <v>37</v>
       </c>
       <c r="I17" s="37">
         <v>25.0</v>
       </c>
-      <c r="J17" s="39" t="s">
+      <c r="J17" s="38" t="s">
         <v>37</v>
       </c>
       <c r="K17" s="46">
         <v>0.5770833333333333</v>
       </c>
-      <c r="L17" s="45"/>
-      <c r="M17" s="45">
+      <c r="L17" s="44"/>
+      <c r="M17" s="44">
         <f>56+41+30</f>
         <v>127</v>
       </c>
-      <c r="N17" s="45">
+      <c r="N17" s="44">
         <v>46.0</v>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="48"/>
+      <c r="J18" s="50"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>

--- a/processing_scripts/Inventory_Processing/2022 Metadata Creation/T4 TMP Data Sheet.xlsx
+++ b/processing_scripts/Inventory_Processing/2022 Metadata Creation/T4 TMP Data Sheet.xlsx
@@ -30,24 +30,24 @@
     <t>End:</t>
   </si>
   <si>
+    <t>NA</t>
+  </si>
+  <si>
     <t>Personnel:</t>
   </si>
   <si>
     <t>AES</t>
   </si>
   <si>
+    <t>EP</t>
+  </si>
+  <si>
     <t>MKB</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
     <t>Depth: 15cm</t>
   </si>
   <si>
-    <t>EP</t>
-  </si>
-  <si>
     <t>Plot</t>
   </si>
   <si>
@@ -102,34 +102,34 @@
     <t>Notes</t>
   </si>
   <si>
+    <t>Total volume</t>
+  </si>
+  <si>
+    <t>Total Vol</t>
+  </si>
+  <si>
+    <t>Evacuated (cb)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROL </t>
+  </si>
+  <si>
+    <t>FRESHWATER</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
     <t>Total Volume</t>
   </si>
   <si>
-    <t>Evacuated (cb)</t>
+    <t>C6</t>
   </si>
   <si>
     <t>SEAWATER</t>
-  </si>
-  <si>
-    <t>Total volume</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROL </t>
-  </si>
-  <si>
-    <t>Total Vol</t>
-  </si>
-  <si>
-    <t>FRESHWATER</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>C6</t>
   </si>
   <si>
     <t>F4</t>
@@ -161,8 +161,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
-    <numFmt numFmtId="165" formatCode="M/d/yyyy"/>
+    <numFmt numFmtId="164" formatCode="M/d/yyyy"/>
+    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="166" formatCode="h&quot;:&quot;mm"/>
   </numFmts>
   <fonts count="5">
@@ -199,6 +199,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF00DA63"/>
+        <bgColor rgb="FF00DA63"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor theme="4"/>
       </patternFill>
@@ -207,12 +213,6 @@
       <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00DA63"/>
-        <bgColor rgb="FF00DA63"/>
       </patternFill>
     </fill>
     <fill>
@@ -346,10 +346,10 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -365,10 +365,10 @@
     <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -416,58 +416,58 @@
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
     <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -535,7 +535,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C8:N17" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C8:N17" displayName="Table_1" name="Table_1" id="2">
   <tableColumns count="12">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -555,7 +555,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D8:N17" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D8:N17" displayName="Table_2" name="Table_2" id="3">
   <tableColumns count="11">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -574,7 +574,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C8:N17" displayName="Table_3" name="Table_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C8:N17" displayName="Table_3" name="Table_3" id="1">
   <tableColumns count="12">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -834,20 +834,20 @@
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>44736.0</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <v>0.5</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -860,10 +860,10 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -880,7 +880,7 @@
     </row>
     <row r="5">
       <c r="A5" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -897,10 +897,10 @@
       <c r="N5" s="3"/>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="16" t="s">
@@ -962,172 +962,172 @@
         <v>28</v>
       </c>
       <c r="M7" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" s="32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="32" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="35" t="s">
+      <c r="B8" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="34" t="s">
-        <v>33</v>
-      </c>
       <c r="C8" s="37" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E8" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G8" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H8" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I8" s="37" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J8" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="K8" s="41"/>
-      <c r="L8" s="41" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+      <c r="K8" s="39"/>
+      <c r="L8" s="39" t="s">
+        <v>35</v>
       </c>
       <c r="M8" s="38">
         <v>0.0</v>
       </c>
       <c r="N8" s="38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="40" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="42" t="s">
-        <v>38</v>
-      </c>
       <c r="C9" s="43" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D9" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F9" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G9" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H9" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I9" s="43" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J9" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+      <c r="K9" s="39"/>
+      <c r="L9" s="39" t="s">
+        <v>35</v>
       </c>
       <c r="M9" s="44">
         <v>0.0</v>
       </c>
       <c r="N9" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="34" t="s">
+      <c r="A10" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="35" t="s">
         <v>39</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E10" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H10" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J10" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39" t="s">
+        <v>35</v>
       </c>
       <c r="M10" s="38" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N10" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="42" t="s">
+      <c r="A11" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="40" t="s">
         <v>40</v>
       </c>
       <c r="C11" s="43">
         <v>10.0</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E11" s="44">
         <v>1.5</v>
       </c>
       <c r="F11" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H11" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I11" s="43">
         <v>12.5</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="K11" s="41"/>
-      <c r="L11" s="41" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+      <c r="K11" s="39"/>
+      <c r="L11" s="39" t="s">
+        <v>35</v>
       </c>
       <c r="M11" s="44">
         <v>24.0</v>
@@ -1137,39 +1137,39 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="34" t="s">
+      <c r="A12" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="35" t="s">
         <v>41</v>
       </c>
       <c r="C12" s="37">
         <v>10.0</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E12" s="38">
         <v>1.5</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H12" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I12" s="37">
         <v>25.0</v>
       </c>
       <c r="J12" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="K12" s="41"/>
-      <c r="L12" s="41" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+      <c r="K12" s="39"/>
+      <c r="L12" s="39" t="s">
+        <v>35</v>
       </c>
       <c r="M12" s="38">
         <v>40.0</v>
@@ -1179,81 +1179,81 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="42" t="s">
+      <c r="A13" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="40" t="s">
         <v>42</v>
       </c>
       <c r="C13" s="43" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H13" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I13" s="43" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J13" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="K13" s="41"/>
-      <c r="L13" s="41" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+      <c r="K13" s="39"/>
+      <c r="L13" s="39" t="s">
+        <v>35</v>
       </c>
       <c r="M13" s="44">
         <v>0.0</v>
       </c>
       <c r="N13" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="34" t="s">
+      <c r="A14" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="35" t="s">
         <v>43</v>
       </c>
       <c r="C14" s="37">
         <v>10.0</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E14" s="38">
         <v>1.5</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H14" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I14" s="37">
         <v>25.0</v>
       </c>
       <c r="J14" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="K14" s="41"/>
-      <c r="L14" s="41" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39" t="s">
+        <v>35</v>
       </c>
       <c r="M14" s="38">
         <v>42.0</v>
@@ -1263,81 +1263,81 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="42" t="s">
+      <c r="A15" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="40" t="s">
         <v>44</v>
       </c>
       <c r="C15" s="43">
         <v>7.0</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E15" s="44">
         <v>1.5</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G15" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H15" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="I15" s="47">
+        <v>35</v>
+      </c>
+      <c r="I15" s="46">
         <v>1.5</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="K15" s="41"/>
-      <c r="L15" s="41" t="s">
-        <v>37</v>
-      </c>
-      <c r="M15" s="49">
+        <v>35</v>
+      </c>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="M15" s="48">
         <v>11.0</v>
       </c>
       <c r="N15" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="34" t="s">
+      <c r="A16" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="35" t="s">
         <v>45</v>
       </c>
       <c r="C16" s="37">
         <v>10.0</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E16" s="38">
         <v>1.5</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H16" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I16" s="37">
         <v>17.5</v>
       </c>
       <c r="J16" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="K16" s="41"/>
-      <c r="L16" s="41" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+      <c r="K16" s="39"/>
+      <c r="L16" s="39" t="s">
+        <v>35</v>
       </c>
       <c r="M16" s="38">
         <v>29.0</v>
@@ -1347,39 +1347,39 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="42" t="s">
+      <c r="A17" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="40" t="s">
         <v>46</v>
       </c>
       <c r="C17" s="43">
         <v>10.0</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E17" s="44">
         <v>1.5</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H17" s="44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I17" s="43">
         <v>25.0</v>
       </c>
       <c r="J17" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="K17" s="41"/>
-      <c r="L17" s="41" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+      <c r="K17" s="39"/>
+      <c r="L17" s="39" t="s">
+        <v>35</v>
       </c>
       <c r="M17" s="44">
         <v>42.0</v>
@@ -1398,7 +1398,7 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="50"/>
+      <c r="J18" s="49"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -1528,19 +1528,19 @@
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="6">
         <v>44736.0</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="8">
         <v>0.5111111111111111</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="8">
         <v>0.5666666666666667</v>
       </c>
       <c r="G3" s="2"/>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -1572,7 +1572,7 @@
     </row>
     <row r="5">
       <c r="A5" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -1589,10 +1589,10 @@
       <c r="N5" s="11"/>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="16" t="s">
@@ -1654,430 +1654,430 @@
         <v>28</v>
       </c>
       <c r="M7" s="31" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N7" s="32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="34" t="s">
+      <c r="A8" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="39">
+      <c r="B8" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="36">
         <v>10.0</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E8" s="38">
         <v>1.5</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G8" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H8" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I8" s="37">
         <v>25.0</v>
       </c>
       <c r="J8" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K8" s="38"/>
       <c r="L8" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M8" s="38">
         <v>36.5</v>
       </c>
       <c r="N8" s="38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="40" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="45">
+      <c r="C9" s="42">
         <v>10.0</v>
       </c>
       <c r="D9" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E9" s="44">
         <v>1.5</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G9" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H9" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I9" s="43">
         <v>16.0</v>
       </c>
       <c r="J9" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K9" s="38"/>
       <c r="L9" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M9" s="44">
         <v>27.5</v>
       </c>
       <c r="N9" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="34" t="s">
+      <c r="A10" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="39">
+      <c r="C10" s="36">
         <v>10.0</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E10" s="38">
         <v>1.5</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H10" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I10" s="37">
         <v>25.0</v>
       </c>
       <c r="J10" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K10" s="38"/>
       <c r="L10" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M10" s="38">
         <v>36.5</v>
       </c>
       <c r="N10" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="42" t="s">
+      <c r="A11" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="45">
+      <c r="C11" s="42">
         <v>10.0</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E11" s="44">
         <v>1.5</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G11" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H11" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I11" s="43">
         <v>25.0</v>
       </c>
       <c r="J11" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K11" s="38"/>
       <c r="L11" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M11" s="38">
         <v>36.5</v>
       </c>
       <c r="N11" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="34" t="s">
+      <c r="A12" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="39">
+      <c r="C12" s="36">
         <v>10.0</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E12" s="38">
         <v>1.5</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H12" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I12" s="37">
         <v>25.0</v>
       </c>
       <c r="J12" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K12" s="38"/>
       <c r="L12" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M12" s="38">
         <v>36.5</v>
       </c>
       <c r="N12" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="42" t="s">
+      <c r="A13" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="45">
+      <c r="C13" s="42">
         <v>10.0</v>
       </c>
       <c r="D13" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E13" s="44">
         <v>1.5</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I13" s="43">
         <v>25.0</v>
       </c>
       <c r="J13" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K13" s="38"/>
       <c r="L13" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M13" s="38">
         <v>36.5</v>
       </c>
       <c r="N13" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="34" t="s">
+      <c r="A14" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="39">
+      <c r="C14" s="36">
         <v>10.0</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E14" s="38">
         <v>1.5</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H14" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I14" s="37">
         <v>25.0</v>
       </c>
       <c r="J14" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K14" s="38"/>
       <c r="L14" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M14" s="38">
         <v>36.5</v>
       </c>
       <c r="N14" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="42" t="s">
+      <c r="A15" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="45">
+      <c r="C15" s="42">
         <v>10.0</v>
       </c>
       <c r="D15" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E15" s="44">
         <v>1.5</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G15" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H15" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I15" s="43">
         <v>25.0</v>
       </c>
       <c r="J15" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K15" s="38"/>
       <c r="L15" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M15" s="38">
         <v>36.5</v>
       </c>
       <c r="N15" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="34" t="s">
+      <c r="A16" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="39">
+      <c r="C16" s="36">
         <v>10.0</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E16" s="38">
         <v>1.5</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H16" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I16" s="37">
         <v>25.0</v>
       </c>
       <c r="J16" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K16" s="38"/>
       <c r="L16" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M16" s="38">
         <v>36.5</v>
       </c>
       <c r="N16" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="42" t="s">
+      <c r="A17" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="45">
+      <c r="C17" s="42">
         <v>10.0</v>
       </c>
       <c r="D17" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E17" s="44">
         <v>1.5</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G17" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H17" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I17" s="43">
         <v>25.0</v>
       </c>
       <c r="J17" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K17" s="38"/>
       <c r="L17" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M17" s="38">
         <v>36.5</v>
       </c>
       <c r="N17" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -2090,7 +2090,7 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="50"/>
+      <c r="J18" s="49"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -2170,19 +2170,19 @@
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="6">
         <v>44736.0</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="8">
         <v>0.5104166666666666</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="8">
         <v>0.58125</v>
       </c>
       <c r="G3" s="2"/>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -2214,7 +2214,7 @@
     </row>
     <row r="5">
       <c r="A5" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -2231,10 +2231,10 @@
       <c r="N5" s="11"/>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="16" t="s">
@@ -2296,44 +2296,44 @@
         <v>28</v>
       </c>
       <c r="M7" s="31" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="N7" s="32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="34" t="s">
-        <v>33</v>
+      <c r="A8" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>34</v>
       </c>
       <c r="C8" s="37">
         <v>10.0</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E8" s="38">
         <v>1.5</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G8" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H8" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I8" s="37">
         <v>25.0</v>
       </c>
       <c r="J8" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="K8" s="40">
+        <v>35</v>
+      </c>
+      <c r="K8" s="45">
         <v>0.5111111111111111</v>
       </c>
       <c r="L8" s="38"/>
@@ -2346,37 +2346,37 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="42" t="s">
+      <c r="A9" s="41" t="s">
         <v>38</v>
+      </c>
+      <c r="B9" s="40" t="s">
+        <v>37</v>
       </c>
       <c r="C9" s="37">
         <v>10.0</v>
       </c>
       <c r="D9" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E9" s="38">
         <v>1.5</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G9" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H9" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I9" s="37">
         <v>25.0</v>
       </c>
       <c r="J9" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="K9" s="46">
+        <v>35</v>
+      </c>
+      <c r="K9" s="47">
         <v>0.51875</v>
       </c>
       <c r="L9" s="44"/>
@@ -2389,37 +2389,37 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="34" t="s">
+      <c r="A10" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="35" t="s">
         <v>39</v>
       </c>
       <c r="C10" s="37">
         <v>10.0</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E10" s="38">
         <v>1.5</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H10" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I10" s="37">
         <v>25.0</v>
       </c>
       <c r="J10" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="K10" s="40">
+        <v>35</v>
+      </c>
+      <c r="K10" s="45">
         <v>0.5277777777777778</v>
       </c>
       <c r="L10" s="38"/>
@@ -2432,37 +2432,37 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="42" t="s">
+      <c r="A11" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="40" t="s">
         <v>40</v>
       </c>
       <c r="C11" s="37">
         <v>10.0</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E11" s="38">
         <v>1.5</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G11" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H11" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I11" s="37">
         <v>25.0</v>
       </c>
       <c r="J11" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="K11" s="46">
+        <v>35</v>
+      </c>
+      <c r="K11" s="47">
         <v>0.5340277777777778</v>
       </c>
       <c r="L11" s="44"/>
@@ -2475,37 +2475,37 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="34" t="s">
+      <c r="A12" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="35" t="s">
         <v>41</v>
       </c>
       <c r="C12" s="37">
         <v>10.0</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E12" s="38">
         <v>1.5</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H12" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I12" s="37">
         <v>25.0</v>
       </c>
       <c r="J12" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="K12" s="40">
+        <v>35</v>
+      </c>
+      <c r="K12" s="45">
         <v>0.5416666666666666</v>
       </c>
       <c r="L12" s="38"/>
@@ -2518,41 +2518,41 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="42" t="s">
+      <c r="A13" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="40" t="s">
         <v>42</v>
       </c>
       <c r="C13" s="37">
         <v>10.0</v>
       </c>
       <c r="D13" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E13" s="38">
         <v>1.5</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I13" s="37">
         <v>25.0</v>
       </c>
       <c r="J13" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="K13" s="46">
+        <v>35</v>
+      </c>
+      <c r="K13" s="47">
         <v>0.5486111111111112</v>
       </c>
       <c r="L13" s="44"/>
-      <c r="M13" s="48">
+      <c r="M13" s="50">
         <f>53+55+20</f>
         <v>128</v>
       </c>
@@ -2561,37 +2561,37 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="34" t="s">
+      <c r="A14" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="35" t="s">
         <v>43</v>
       </c>
       <c r="C14" s="37">
         <v>10.0</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E14" s="38">
         <v>1.5</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H14" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I14" s="37">
         <v>25.0</v>
       </c>
       <c r="J14" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="K14" s="40">
+        <v>35</v>
+      </c>
+      <c r="K14" s="45">
         <v>0.5555555555555556</v>
       </c>
       <c r="L14" s="38"/>
@@ -2604,37 +2604,37 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="42" t="s">
+      <c r="A15" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="40" t="s">
         <v>44</v>
       </c>
       <c r="C15" s="37">
         <v>10.0</v>
       </c>
       <c r="D15" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E15" s="38">
         <v>1.5</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G15" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H15" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I15" s="37">
         <v>25.0</v>
       </c>
       <c r="J15" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="K15" s="46">
+        <v>35</v>
+      </c>
+      <c r="K15" s="47">
         <v>0.5625</v>
       </c>
       <c r="L15" s="44"/>
@@ -2647,37 +2647,37 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="34" t="s">
+      <c r="A16" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="35" t="s">
         <v>45</v>
       </c>
       <c r="C16" s="37">
         <v>10.0</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E16" s="38">
         <v>1.5</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H16" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I16" s="37">
         <v>25.0</v>
       </c>
       <c r="J16" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="K16" s="40">
+        <v>35</v>
+      </c>
+      <c r="K16" s="45">
         <v>0.5694444444444444</v>
       </c>
       <c r="L16" s="38"/>
@@ -2690,37 +2690,37 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="42" t="s">
+      <c r="A17" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="40" t="s">
         <v>46</v>
       </c>
       <c r="C17" s="37">
         <v>10.0</v>
       </c>
       <c r="D17" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E17" s="38">
         <v>1.5</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G17" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H17" s="38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I17" s="37">
         <v>25.0</v>
       </c>
       <c r="J17" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="K17" s="46">
+        <v>35</v>
+      </c>
+      <c r="K17" s="47">
         <v>0.5770833333333333</v>
       </c>
       <c r="L17" s="44"/>
@@ -2742,7 +2742,7 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="50"/>
+      <c r="J18" s="49"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>

--- a/processing_scripts/Inventory_Processing/2022 Metadata Creation/T4 TMP Data Sheet.xlsx
+++ b/processing_scripts/Inventory_Processing/2022 Metadata Creation/T4 TMP Data Sheet.xlsx
@@ -30,24 +30,24 @@
     <t>End:</t>
   </si>
   <si>
+    <t>Personnel:</t>
+  </si>
+  <si>
+    <t>MKB</t>
+  </si>
+  <si>
     <t>NA</t>
   </si>
   <si>
-    <t>Personnel:</t>
+    <t>Depth: 15cm</t>
+  </si>
+  <si>
+    <t>EP</t>
   </si>
   <si>
     <t>AES</t>
   </si>
   <si>
-    <t>EP</t>
-  </si>
-  <si>
-    <t>MKB</t>
-  </si>
-  <si>
-    <t>Depth: 15cm</t>
-  </si>
-  <si>
     <t>Plot</t>
   </si>
   <si>
@@ -102,19 +102,25 @@
     <t>Notes</t>
   </si>
   <si>
+    <t>Total Vol</t>
+  </si>
+  <si>
     <t>Total volume</t>
   </si>
   <si>
-    <t>Total Vol</t>
+    <t>Total Volume</t>
   </si>
   <si>
     <t>Evacuated (cb)</t>
   </si>
   <si>
+    <t>FRESHWATER</t>
+  </si>
+  <si>
     <t xml:space="preserve">CONTROL </t>
   </si>
   <si>
-    <t>FRESHWATER</t>
+    <t>SEAWATER</t>
   </si>
   <si>
     <t>C3</t>
@@ -123,13 +129,7 @@
     <t>—</t>
   </si>
   <si>
-    <t>Total Volume</t>
-  </si>
-  <si>
     <t>C6</t>
-  </si>
-  <si>
-    <t>SEAWATER</t>
   </si>
   <si>
     <t>F4</t>
@@ -161,8 +161,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="M/d/yyyy"/>
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="165" formatCode="M/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="h&quot;:&quot;mm"/>
   </numFmts>
   <fonts count="5">
@@ -199,8 +199,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00DA63"/>
-        <bgColor rgb="FF00DA63"/>
+        <fgColor theme="5"/>
+        <bgColor theme="5"/>
       </patternFill>
     </fill>
     <fill>
@@ -211,8 +211,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor theme="5"/>
+        <fgColor rgb="FF00DA63"/>
+        <bgColor rgb="FF00DA63"/>
       </patternFill>
     </fill>
     <fill>
@@ -346,10 +346,10 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -365,10 +365,10 @@
     <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -395,16 +395,16 @@
     </xf>
     <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -416,58 +416,58 @@
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -502,15 +502,15 @@
     </dxf>
   </dxfs>
   <tableStyles count="3">
-    <tableStyle count="2" pivot="0" name="CONTROL-style">
-      <tableStyleElement dxfId="1" type="firstRowStripe"/>
-      <tableStyleElement dxfId="2" type="secondRowStripe"/>
-    </tableStyle>
     <tableStyle count="2" pivot="0" name="FRESHWATER-style">
       <tableStyleElement dxfId="1" type="firstRowStripe"/>
       <tableStyleElement dxfId="2" type="secondRowStripe"/>
     </tableStyle>
     <tableStyle count="2" pivot="0" name="SEAWATER-style">
+      <tableStyleElement dxfId="1" type="firstRowStripe"/>
+      <tableStyleElement dxfId="2" type="secondRowStripe"/>
+    </tableStyle>
+    <tableStyle count="2" pivot="0" name="CONTROL-style">
       <tableStyleElement dxfId="1" type="firstRowStripe"/>
       <tableStyleElement dxfId="2" type="secondRowStripe"/>
     </tableStyle>
@@ -535,7 +535,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C8:N17" displayName="Table_1" name="Table_1" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C8:N17" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="12">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -555,7 +555,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D8:N17" displayName="Table_2" name="Table_2" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D8:N17" displayName="Table_3" name="Table_3" id="3">
   <tableColumns count="11">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -574,7 +574,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C8:N17" displayName="Table_3" name="Table_3" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C8:N17" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="12">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -834,20 +834,20 @@
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="6">
         <v>44736.0</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="8">
         <v>0.5</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -860,10 +860,10 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -880,7 +880,7 @@
     </row>
     <row r="5">
       <c r="A5" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -897,10 +897,10 @@
       <c r="N5" s="3"/>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="16" t="s">
@@ -962,172 +962,172 @@
         <v>28</v>
       </c>
       <c r="M7" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N7" s="32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="s">
-        <v>32</v>
+      <c r="A8" s="34" t="s">
+        <v>34</v>
       </c>
       <c r="B8" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="M8" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="N8" s="39" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="J8" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="39"/>
-      <c r="L8" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="M8" s="38">
-        <v>0.0</v>
-      </c>
-      <c r="N8" s="38" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="43" t="s">
-        <v>35</v>
+      <c r="B9" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="45" t="s">
+        <v>37</v>
       </c>
       <c r="D9" s="44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F9" s="44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G9" s="44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H9" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="I9" s="43" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I9" s="45" t="s">
+        <v>37</v>
       </c>
       <c r="J9" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="K9" s="39"/>
-      <c r="L9" s="39" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42" t="s">
+        <v>37</v>
       </c>
       <c r="M9" s="44">
         <v>0.0</v>
       </c>
       <c r="N9" s="44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="s">
-        <v>32</v>
+      <c r="A10" s="34" t="s">
+        <v>34</v>
       </c>
       <c r="B10" s="35" t="s">
         <v>39</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" s="38" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K10" s="39"/>
-      <c r="L10" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="M10" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="N10" s="38" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="J10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" s="42"/>
+      <c r="L10" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="N10" s="39" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="40" t="s">
+      <c r="A11" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="43">
+      <c r="C11" s="45">
         <v>10.0</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E11" s="44">
         <v>1.5</v>
       </c>
       <c r="F11" s="44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H11" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" s="43">
+        <v>37</v>
+      </c>
+      <c r="I11" s="45">
         <v>12.5</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42" t="s">
+        <v>37</v>
       </c>
       <c r="M11" s="44">
         <v>24.0</v>
@@ -1137,8 +1137,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="s">
-        <v>32</v>
+      <c r="A12" s="34" t="s">
+        <v>34</v>
       </c>
       <c r="B12" s="35" t="s">
         <v>41</v>
@@ -1146,83 +1146,83 @@
       <c r="C12" s="37">
         <v>10.0</v>
       </c>
-      <c r="D12" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="38">
+      <c r="D12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="39">
         <v>1.5</v>
       </c>
-      <c r="F12" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" s="38" t="s">
-        <v>35</v>
+      <c r="F12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="I12" s="37">
         <v>25.0</v>
       </c>
-      <c r="J12" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="M12" s="38">
+      <c r="J12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" s="42"/>
+      <c r="L12" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="M12" s="39">
         <v>40.0</v>
       </c>
-      <c r="N12" s="38">
+      <c r="N12" s="39">
         <v>50.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="40" t="s">
+      <c r="A13" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="43" t="s">
-        <v>35</v>
+      <c r="C13" s="45" t="s">
+        <v>37</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H13" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="I13" s="43" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="I13" s="45" t="s">
+        <v>37</v>
       </c>
       <c r="J13" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="K13" s="39"/>
-      <c r="L13" s="39" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42" t="s">
+        <v>37</v>
       </c>
       <c r="M13" s="44">
         <v>0.0</v>
       </c>
       <c r="N13" s="44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="s">
-        <v>32</v>
+      <c r="A14" s="34" t="s">
+        <v>34</v>
       </c>
       <c r="B14" s="35" t="s">
         <v>43</v>
@@ -1230,83 +1230,83 @@
       <c r="C14" s="37">
         <v>10.0</v>
       </c>
-      <c r="D14" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="38">
+      <c r="D14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="39">
         <v>1.5</v>
       </c>
-      <c r="F14" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H14" s="38" t="s">
-        <v>35</v>
+      <c r="F14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="I14" s="37">
         <v>25.0</v>
       </c>
-      <c r="J14" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K14" s="39"/>
-      <c r="L14" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="M14" s="38">
+      <c r="J14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="M14" s="39">
         <v>42.0</v>
       </c>
-      <c r="N14" s="38">
+      <c r="N14" s="39">
         <v>50.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="40" t="s">
+      <c r="A15" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="43">
+      <c r="C15" s="45">
         <v>7.0</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E15" s="44">
         <v>1.5</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G15" s="44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H15" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" s="46">
+        <v>37</v>
+      </c>
+      <c r="I15" s="48">
         <v>1.5</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="K15" s="39"/>
-      <c r="L15" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="M15" s="48">
+        <v>37</v>
+      </c>
+      <c r="K15" s="42"/>
+      <c r="L15" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="M15" s="49">
         <v>11.0</v>
       </c>
       <c r="N15" s="44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="33" t="s">
-        <v>32</v>
+      <c r="A16" s="34" t="s">
+        <v>34</v>
       </c>
       <c r="B16" s="35" t="s">
         <v>45</v>
@@ -1314,72 +1314,72 @@
       <c r="C16" s="37">
         <v>10.0</v>
       </c>
-      <c r="D16" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="38">
+      <c r="D16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="39">
         <v>1.5</v>
       </c>
-      <c r="F16" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H16" s="38" t="s">
-        <v>35</v>
+      <c r="F16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="I16" s="37">
         <v>17.5</v>
       </c>
-      <c r="J16" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K16" s="39"/>
-      <c r="L16" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="M16" s="38">
+      <c r="J16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" s="42"/>
+      <c r="L16" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="M16" s="39">
         <v>29.0</v>
       </c>
-      <c r="N16" s="38">
+      <c r="N16" s="39">
         <v>50.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="40" t="s">
+      <c r="A17" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="43">
+      <c r="C17" s="45">
         <v>10.0</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E17" s="44">
         <v>1.5</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H17" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="I17" s="43">
+        <v>37</v>
+      </c>
+      <c r="I17" s="45">
         <v>25.0</v>
       </c>
       <c r="J17" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="K17" s="39"/>
-      <c r="L17" s="39" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="K17" s="42"/>
+      <c r="L17" s="42" t="s">
+        <v>37</v>
       </c>
       <c r="M17" s="44">
         <v>42.0</v>
@@ -1398,7 +1398,7 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="49"/>
+      <c r="J18" s="50"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -1528,19 +1528,19 @@
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>44736.0</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <v>0.5111111111111111</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="7">
         <v>0.5666666666666667</v>
       </c>
       <c r="G3" s="2"/>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -1572,7 +1572,7 @@
     </row>
     <row r="5">
       <c r="A5" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -1592,7 +1592,7 @@
       <c r="A6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="16" t="s">
@@ -1654,98 +1654,98 @@
         <v>28</v>
       </c>
       <c r="M7" s="31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N7" s="32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="33" t="s">
         <v>33</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8" s="36">
         <v>10.0</v>
       </c>
-      <c r="D8" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="38">
+      <c r="D8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="39">
         <v>1.5</v>
       </c>
-      <c r="F8" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="38" t="s">
-        <v>35</v>
+      <c r="F8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="I8" s="37">
         <v>25.0</v>
       </c>
-      <c r="J8" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="M8" s="38">
+      <c r="J8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="39"/>
+      <c r="L8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="M8" s="39">
         <v>36.5</v>
       </c>
-      <c r="N8" s="38" t="s">
-        <v>35</v>
+      <c r="N8" s="39" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="42">
+      <c r="B9" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="43">
         <v>10.0</v>
       </c>
-      <c r="D9" s="38" t="s">
-        <v>35</v>
+      <c r="D9" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="E9" s="44">
         <v>1.5</v>
       </c>
-      <c r="F9" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="I9" s="43">
+      <c r="F9" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" s="45">
         <v>16.0</v>
       </c>
-      <c r="J9" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K9" s="38"/>
-      <c r="L9" s="38" t="s">
-        <v>35</v>
+      <c r="J9" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="39"/>
+      <c r="L9" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="M9" s="44">
         <v>27.5</v>
       </c>
-      <c r="N9" s="38" t="s">
-        <v>35</v>
+      <c r="N9" s="39" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="33" t="s">
         <v>33</v>
       </c>
       <c r="B10" s="35" t="s">
@@ -1754,82 +1754,82 @@
       <c r="C10" s="36">
         <v>10.0</v>
       </c>
-      <c r="D10" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="38">
+      <c r="D10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="39">
         <v>1.5</v>
       </c>
-      <c r="F10" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" s="38" t="s">
-        <v>35</v>
+      <c r="F10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="I10" s="37">
         <v>25.0</v>
       </c>
-      <c r="J10" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K10" s="38"/>
-      <c r="L10" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="M10" s="38">
+      <c r="J10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10" s="39">
         <v>36.5</v>
       </c>
-      <c r="N10" s="38" t="s">
-        <v>35</v>
+      <c r="N10" s="39" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="42">
+      <c r="C11" s="43">
         <v>10.0</v>
       </c>
-      <c r="D11" s="38" t="s">
-        <v>35</v>
+      <c r="D11" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="E11" s="44">
         <v>1.5</v>
       </c>
-      <c r="F11" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H11" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" s="43">
+      <c r="F11" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="45">
         <v>25.0</v>
       </c>
-      <c r="J11" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="M11" s="38">
+      <c r="J11" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" s="39"/>
+      <c r="L11" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="M11" s="39">
         <v>36.5</v>
       </c>
-      <c r="N11" s="38" t="s">
-        <v>35</v>
+      <c r="N11" s="39" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="33" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="35" t="s">
@@ -1838,82 +1838,82 @@
       <c r="C12" s="36">
         <v>10.0</v>
       </c>
-      <c r="D12" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="38">
+      <c r="D12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="39">
         <v>1.5</v>
       </c>
-      <c r="F12" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" s="38" t="s">
-        <v>35</v>
+      <c r="F12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="I12" s="37">
         <v>25.0</v>
       </c>
-      <c r="J12" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="M12" s="38">
+      <c r="J12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" s="39"/>
+      <c r="L12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="M12" s="39">
         <v>36.5</v>
       </c>
-      <c r="N12" s="38" t="s">
-        <v>35</v>
+      <c r="N12" s="39" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="s">
+      <c r="A13" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="42">
+      <c r="C13" s="43">
         <v>10.0</v>
       </c>
-      <c r="D13" s="38" t="s">
-        <v>35</v>
+      <c r="D13" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="E13" s="44">
         <v>1.5</v>
       </c>
-      <c r="F13" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H13" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="I13" s="43">
+      <c r="F13" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="45">
         <v>25.0</v>
       </c>
-      <c r="J13" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K13" s="38"/>
-      <c r="L13" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="M13" s="38">
+      <c r="J13" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" s="39"/>
+      <c r="L13" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="M13" s="39">
         <v>36.5</v>
       </c>
-      <c r="N13" s="38" t="s">
-        <v>35</v>
+      <c r="N13" s="39" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="33" t="s">
         <v>33</v>
       </c>
       <c r="B14" s="35" t="s">
@@ -1922,82 +1922,82 @@
       <c r="C14" s="36">
         <v>10.0</v>
       </c>
-      <c r="D14" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="38">
+      <c r="D14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="39">
         <v>1.5</v>
       </c>
-      <c r="F14" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H14" s="38" t="s">
-        <v>35</v>
+      <c r="F14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="I14" s="37">
         <v>25.0</v>
       </c>
-      <c r="J14" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K14" s="38"/>
-      <c r="L14" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="M14" s="38">
+      <c r="J14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="M14" s="39">
         <v>36.5</v>
       </c>
-      <c r="N14" s="38" t="s">
-        <v>35</v>
+      <c r="N14" s="39" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="42">
+      <c r="C15" s="43">
         <v>10.0</v>
       </c>
-      <c r="D15" s="38" t="s">
-        <v>35</v>
+      <c r="D15" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="E15" s="44">
         <v>1.5</v>
       </c>
-      <c r="F15" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H15" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" s="43">
+      <c r="F15" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="45">
         <v>25.0</v>
       </c>
-      <c r="J15" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K15" s="38"/>
-      <c r="L15" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="M15" s="38">
+      <c r="J15" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="M15" s="39">
         <v>36.5</v>
       </c>
-      <c r="N15" s="38" t="s">
-        <v>35</v>
+      <c r="N15" s="39" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="33" t="s">
         <v>33</v>
       </c>
       <c r="B16" s="35" t="s">
@@ -2006,78 +2006,78 @@
       <c r="C16" s="36">
         <v>10.0</v>
       </c>
-      <c r="D16" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="38">
+      <c r="D16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="39">
         <v>1.5</v>
       </c>
-      <c r="F16" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H16" s="38" t="s">
-        <v>35</v>
+      <c r="F16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="I16" s="37">
         <v>25.0</v>
       </c>
-      <c r="J16" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K16" s="38"/>
-      <c r="L16" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="M16" s="38">
+      <c r="J16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" s="39"/>
+      <c r="L16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="M16" s="39">
         <v>36.5</v>
       </c>
-      <c r="N16" s="38" t="s">
-        <v>35</v>
+      <c r="N16" s="39" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="s">
+      <c r="A17" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="42">
+      <c r="C17" s="43">
         <v>10.0</v>
       </c>
-      <c r="D17" s="38" t="s">
-        <v>35</v>
+      <c r="D17" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="E17" s="44">
         <v>1.5</v>
       </c>
-      <c r="F17" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H17" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="I17" s="43">
+      <c r="F17" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="45">
         <v>25.0</v>
       </c>
-      <c r="J17" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K17" s="38"/>
-      <c r="L17" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="M17" s="38">
+      <c r="J17" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" s="39"/>
+      <c r="L17" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="M17" s="39">
         <v>36.5</v>
       </c>
-      <c r="N17" s="38" t="s">
-        <v>35</v>
+      <c r="N17" s="39" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -2090,7 +2090,7 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="49"/>
+      <c r="J18" s="50"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -2170,19 +2170,19 @@
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>44736.0</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <v>0.5104166666666666</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="7">
         <v>0.58125</v>
       </c>
       <c r="G3" s="2"/>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>9</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -2214,7 +2214,7 @@
     </row>
     <row r="5">
       <c r="A5" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -2231,10 +2231,10 @@
       <c r="N5" s="11"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="16" t="s">
@@ -2296,87 +2296,87 @@
         <v>28</v>
       </c>
       <c r="M7" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="N7" s="32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="35" t="s">
         <v>36</v>
-      </c>
-      <c r="N7" s="32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>34</v>
       </c>
       <c r="C8" s="37">
         <v>10.0</v>
       </c>
-      <c r="D8" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="38">
+      <c r="D8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="39">
         <v>1.5</v>
       </c>
-      <c r="F8" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="38" t="s">
-        <v>35</v>
+      <c r="F8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="I8" s="37">
         <v>25.0</v>
       </c>
-      <c r="J8" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="45">
+      <c r="J8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="40">
         <v>0.5111111111111111</v>
       </c>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38">
+      <c r="L8" s="39"/>
+      <c r="M8" s="39">
         <f>58+56+23</f>
         <v>137</v>
       </c>
-      <c r="N8" s="38">
+      <c r="N8" s="39">
         <v>50.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="41" t="s">
         <v>38</v>
-      </c>
-      <c r="B9" s="40" t="s">
-        <v>37</v>
       </c>
       <c r="C9" s="37">
         <v>10.0</v>
       </c>
-      <c r="D9" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="38">
+      <c r="D9" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="39">
         <v>1.5</v>
       </c>
-      <c r="F9" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="38" t="s">
-        <v>35</v>
+      <c r="F9" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="I9" s="37">
         <v>25.0</v>
       </c>
-      <c r="J9" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K9" s="47">
+      <c r="J9" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="46">
         <v>0.51875</v>
       </c>
       <c r="L9" s="44"/>
@@ -2389,8 +2389,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="41" t="s">
-        <v>38</v>
+      <c r="A10" s="38" t="s">
+        <v>35</v>
       </c>
       <c r="B10" s="35" t="s">
         <v>39</v>
@@ -2398,71 +2398,71 @@
       <c r="C10" s="37">
         <v>10.0</v>
       </c>
-      <c r="D10" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="38">
+      <c r="D10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="39">
         <v>1.5</v>
       </c>
-      <c r="F10" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" s="38" t="s">
-        <v>35</v>
+      <c r="F10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="I10" s="37">
         <v>25.0</v>
       </c>
-      <c r="J10" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K10" s="45">
+      <c r="J10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" s="40">
         <v>0.5277777777777778</v>
       </c>
-      <c r="L10" s="38"/>
-      <c r="M10" s="38">
+      <c r="L10" s="39"/>
+      <c r="M10" s="39">
         <f>56+19</f>
         <v>75</v>
       </c>
-      <c r="N10" s="38">
+      <c r="N10" s="39">
         <v>47.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="40" t="s">
+      <c r="A11" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="41" t="s">
         <v>40</v>
       </c>
       <c r="C11" s="37">
         <v>10.0</v>
       </c>
-      <c r="D11" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="38">
+      <c r="D11" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="39">
         <v>1.5</v>
       </c>
-      <c r="F11" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H11" s="38" t="s">
-        <v>35</v>
+      <c r="F11" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="I11" s="37">
         <v>25.0</v>
       </c>
-      <c r="J11" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K11" s="47">
+      <c r="J11" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" s="46">
         <v>0.5340277777777778</v>
       </c>
       <c r="L11" s="44"/>
@@ -2475,8 +2475,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="41" t="s">
-        <v>38</v>
+      <c r="A12" s="38" t="s">
+        <v>35</v>
       </c>
       <c r="B12" s="35" t="s">
         <v>41</v>
@@ -2484,75 +2484,75 @@
       <c r="C12" s="37">
         <v>10.0</v>
       </c>
-      <c r="D12" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="38">
+      <c r="D12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="39">
         <v>1.5</v>
       </c>
-      <c r="F12" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" s="38" t="s">
-        <v>35</v>
+      <c r="F12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="I12" s="37">
         <v>25.0</v>
       </c>
-      <c r="J12" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K12" s="45">
+      <c r="J12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" s="40">
         <v>0.5416666666666666</v>
       </c>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38">
+      <c r="L12" s="39"/>
+      <c r="M12" s="39">
         <f>59+50+1</f>
         <v>110</v>
       </c>
-      <c r="N12" s="38">
+      <c r="N12" s="39">
         <v>50.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="40" t="s">
+      <c r="A13" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="41" t="s">
         <v>42</v>
       </c>
       <c r="C13" s="37">
         <v>10.0</v>
       </c>
-      <c r="D13" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" s="38">
+      <c r="D13" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="39">
         <v>1.5</v>
       </c>
-      <c r="F13" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H13" s="38" t="s">
-        <v>35</v>
+      <c r="F13" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="I13" s="37">
         <v>25.0</v>
       </c>
-      <c r="J13" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K13" s="47">
+      <c r="J13" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" s="46">
         <v>0.5486111111111112</v>
       </c>
       <c r="L13" s="44"/>
-      <c r="M13" s="50">
+      <c r="M13" s="47">
         <f>53+55+20</f>
         <v>128</v>
       </c>
@@ -2561,8 +2561,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="41" t="s">
-        <v>38</v>
+      <c r="A14" s="38" t="s">
+        <v>35</v>
       </c>
       <c r="B14" s="35" t="s">
         <v>43</v>
@@ -2570,71 +2570,71 @@
       <c r="C14" s="37">
         <v>10.0</v>
       </c>
-      <c r="D14" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="38">
+      <c r="D14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="39">
         <v>1.5</v>
       </c>
-      <c r="F14" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H14" s="38" t="s">
-        <v>35</v>
+      <c r="F14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="I14" s="37">
         <v>25.0</v>
       </c>
-      <c r="J14" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K14" s="45">
+      <c r="J14" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="40">
         <v>0.5555555555555556</v>
       </c>
-      <c r="L14" s="38"/>
-      <c r="M14" s="38">
+      <c r="L14" s="39"/>
+      <c r="M14" s="39">
         <f>55+51</f>
         <v>106</v>
       </c>
-      <c r="N14" s="38">
+      <c r="N14" s="39">
         <v>47.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="40" t="s">
+      <c r="A15" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="41" t="s">
         <v>44</v>
       </c>
       <c r="C15" s="37">
         <v>10.0</v>
       </c>
-      <c r="D15" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="38">
+      <c r="D15" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="39">
         <v>1.5</v>
       </c>
-      <c r="F15" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H15" s="38" t="s">
-        <v>35</v>
+      <c r="F15" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="I15" s="37">
         <v>25.0</v>
       </c>
-      <c r="J15" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K15" s="47">
+      <c r="J15" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" s="46">
         <v>0.5625</v>
       </c>
       <c r="L15" s="44"/>
@@ -2647,8 +2647,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="41" t="s">
-        <v>38</v>
+      <c r="A16" s="38" t="s">
+        <v>35</v>
       </c>
       <c r="B16" s="35" t="s">
         <v>45</v>
@@ -2656,71 +2656,71 @@
       <c r="C16" s="37">
         <v>10.0</v>
       </c>
-      <c r="D16" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="38">
+      <c r="D16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="39">
         <v>1.5</v>
       </c>
-      <c r="F16" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H16" s="38" t="s">
-        <v>35</v>
+      <c r="F16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="I16" s="37">
         <v>25.0</v>
       </c>
-      <c r="J16" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K16" s="45">
+      <c r="J16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" s="40">
         <v>0.5694444444444444</v>
       </c>
-      <c r="L16" s="38"/>
-      <c r="M16" s="38">
+      <c r="L16" s="39"/>
+      <c r="M16" s="39">
         <f>55+37</f>
         <v>92</v>
       </c>
-      <c r="N16" s="38">
+      <c r="N16" s="39">
         <v>50.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="40" t="s">
+      <c r="A17" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="41" t="s">
         <v>46</v>
       </c>
       <c r="C17" s="37">
         <v>10.0</v>
       </c>
-      <c r="D17" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" s="38">
+      <c r="D17" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="39">
         <v>1.5</v>
       </c>
-      <c r="F17" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="H17" s="38" t="s">
-        <v>35</v>
+      <c r="F17" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="I17" s="37">
         <v>25.0</v>
       </c>
-      <c r="J17" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="K17" s="47">
+      <c r="J17" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" s="46">
         <v>0.5770833333333333</v>
       </c>
       <c r="L17" s="44"/>
@@ -2742,7 +2742,7 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="49"/>
+      <c r="J18" s="50"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
